--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>130015100</v>
       </c>
       <c r="B3" t="n">
-        <v>91378</v>
+        <v>91379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130015120</v>
+        <v>130015086</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,9 +937,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>652193</v>
+        <v>652131</v>
       </c>
       <c r="R4" t="n">
-        <v>6683091</v>
+        <v>6683066</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -982,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130015119</v>
+        <v>130015120</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652211</v>
+        <v>652193</v>
       </c>
       <c r="R5" t="n">
-        <v>6683081</v>
+        <v>6683091</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1097,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,32 +1138,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130015086</v>
+        <v>130015119</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1171,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652131</v>
+        <v>652211</v>
       </c>
       <c r="R6" t="n">
-        <v>6683066</v>
+        <v>6683081</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,7 +1256,7 @@
         <v>130015123</v>
       </c>
       <c r="B7" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>130015107</v>
       </c>
       <c r="B8" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>130015103</v>
       </c>
       <c r="B12" t="n">
-        <v>96239</v>
+        <v>96240</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -904,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130015086</v>
+        <v>130015120</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,13 +937,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>652131</v>
+        <v>652193</v>
       </c>
       <c r="R4" t="n">
-        <v>6683066</v>
+        <v>6683091</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1019,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130015120</v>
+        <v>130015119</v>
       </c>
       <c r="B5" t="n">
         <v>98798</v>
@@ -1066,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652193</v>
+        <v>652211</v>
       </c>
       <c r="R5" t="n">
-        <v>6683091</v>
+        <v>6683081</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1101,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,32 +1134,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130015119</v>
+        <v>130015086</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1171,9 +1167,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652211</v>
+        <v>652131</v>
       </c>
       <c r="R6" t="n">
-        <v>6683081</v>
+        <v>6683066</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1372,46 +1372,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130015107</v>
+        <v>130015094</v>
       </c>
       <c r="B8" t="n">
-        <v>97669</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1419,13 +1419,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>652162</v>
+        <v>652100</v>
       </c>
       <c r="R8" t="n">
-        <v>6683102</v>
+        <v>6683133</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,46 +1491,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130015094</v>
+        <v>130015107</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>97669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1538,13 +1538,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>652100</v>
+        <v>652162</v>
       </c>
       <c r="R9" t="n">
-        <v>6683133</v>
+        <v>6683102</v>
       </c>
       <c r="S9" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -1372,46 +1372,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130015094</v>
+        <v>130015107</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>97669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1419,13 +1419,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>652100</v>
+        <v>652162</v>
       </c>
       <c r="R8" t="n">
-        <v>6683133</v>
+        <v>6683102</v>
       </c>
       <c r="S8" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,46 +1491,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130015107</v>
+        <v>130015094</v>
       </c>
       <c r="B9" t="n">
-        <v>97669</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1538,13 +1538,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>652162</v>
+        <v>652100</v>
       </c>
       <c r="R9" t="n">
-        <v>6683102</v>
+        <v>6683133</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>130015100</v>
       </c>
       <c r="B3" t="n">
-        <v>91379</v>
+        <v>91396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130015120</v>
+        <v>130015086</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,9 +937,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>652193</v>
+        <v>652131</v>
       </c>
       <c r="R4" t="n">
-        <v>6683091</v>
+        <v>6683066</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -982,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130015119</v>
+        <v>130015120</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652211</v>
+        <v>652193</v>
       </c>
       <c r="R5" t="n">
-        <v>6683081</v>
+        <v>6683091</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1097,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,32 +1138,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130015086</v>
+        <v>130015119</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1171,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652131</v>
+        <v>652211</v>
       </c>
       <c r="R6" t="n">
-        <v>6683066</v>
+        <v>6683081</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,7 +1256,7 @@
         <v>130015123</v>
       </c>
       <c r="B7" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,46 +1372,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130015107</v>
+        <v>130015094</v>
       </c>
       <c r="B8" t="n">
-        <v>97669</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1419,13 +1419,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>652162</v>
+        <v>652100</v>
       </c>
       <c r="R8" t="n">
-        <v>6683102</v>
+        <v>6683133</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,46 +1491,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130015094</v>
+        <v>130015107</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>97686</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1538,13 +1538,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>652100</v>
+        <v>652162</v>
       </c>
       <c r="R9" t="n">
-        <v>6683133</v>
+        <v>6683102</v>
       </c>
       <c r="S9" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1851,7 +1851,7 @@
         <v>130015103</v>
       </c>
       <c r="B12" t="n">
-        <v>96240</v>
+        <v>96257</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>130015100</v>
       </c>
       <c r="B3" t="n">
-        <v>91412</v>
+        <v>91414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>130015120</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>130015119</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>130015123</v>
       </c>
       <c r="B7" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>130015107</v>
       </c>
       <c r="B9" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>130015103</v>
       </c>
       <c r="B12" t="n">
-        <v>96273</v>
+        <v>96275</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130015085</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>130015100</v>
       </c>
       <c r="B3" t="n">
-        <v>91414</v>
+        <v>91501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130015086</v>
+        <v>130015120</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,13 +937,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>652131</v>
+        <v>652193</v>
       </c>
       <c r="R4" t="n">
-        <v>6683066</v>
+        <v>6683091</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,32 +1019,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130015120</v>
+        <v>130015086</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1056,9 +1052,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652193</v>
+        <v>652131</v>
       </c>
       <c r="R5" t="n">
-        <v>6683091</v>
+        <v>6683066</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1141,7 @@
         <v>130015119</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>130015123</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>130015094</v>
       </c>
       <c r="B8" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>130015107</v>
       </c>
       <c r="B9" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>130015092</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>130015083</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>130015103</v>
       </c>
       <c r="B12" t="n">
-        <v>96275</v>
+        <v>96362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -1019,32 +1019,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130015086</v>
+        <v>130015119</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,13 +1052,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652131</v>
+        <v>652211</v>
       </c>
       <c r="R5" t="n">
-        <v>6683066</v>
+        <v>6683081</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1101,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,32 +1134,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130015119</v>
+        <v>130015086</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1171,9 +1167,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652211</v>
+        <v>652131</v>
       </c>
       <c r="R6" t="n">
-        <v>6683081</v>
+        <v>6683066</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -1372,46 +1372,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130015094</v>
+        <v>130015107</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>97791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1419,13 +1419,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>652100</v>
+        <v>652162</v>
       </c>
       <c r="R8" t="n">
-        <v>6683133</v>
+        <v>6683102</v>
       </c>
       <c r="S8" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,46 +1491,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130015107</v>
+        <v>130015094</v>
       </c>
       <c r="B9" t="n">
-        <v>97791</v>
+        <v>57985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1538,13 +1538,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>652162</v>
+        <v>652100</v>
       </c>
       <c r="R9" t="n">
-        <v>6683102</v>
+        <v>6683133</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>130015094</v>
       </c>
       <c r="B9" t="n">
-        <v>57985</v>
+        <v>58043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>130015094</v>
       </c>
       <c r="B9" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>130015094</v>
       </c>
       <c r="B9" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>130015094</v>
       </c>
       <c r="B9" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>130015094</v>
       </c>
       <c r="B9" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>130015094</v>
       </c>
       <c r="B9" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56955-2025 artfynd.xlsx
+++ b/artfynd/A 56955-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>130015094</v>
       </c>
       <c r="B9" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
